--- a/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
+++ b/data/a8-import/アフィリエイト案件_転職エージェント図鑑.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16775" windowHeight="8772"/>
+    <workbookView windowWidth="23040" windowHeight="10608"/>
   </bookViews>
   <sheets>
     <sheet name="programs_a26090353299_202609040" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>反映</t>
   </si>
@@ -317,7 +317,7 @@
 &lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC2EM+1PBO36+5YCE+5YJRM" alt=""&gt;</t>
   </si>
   <si>
-    <t xml:space="preserve">◆セールスポイント◆
+    <t>◆セールスポイント◆
 ・代表自身がM&amp;A業界の実務経験者であり、業界の実情を包み隠さず率直にお伝えします。
 ・非公開求人を含むM&amp;A仲介・アドバイザリー領域の厳選求人をご紹介します。
 ・書類添削・面接対策から入社後フォローまで、専任コンサルタントが一貫してサポートします。
@@ -329,8 +329,7 @@
 ◆おススメの提案の仕方◆
 ・「M&amp;A転職エージェントおすすめ比較」記事にて、業界経験者による率直な情報提供という独自性を差別化ポイントとして訴求するのが効果的です。
 ・「M&amp;A業界に転職したい」「M&amp;A仲介 適性」などのキーワードに連動した悩み解決型コンテンツで、ミスマッチ防止の誠実さをアピールしてください。
-・「年収1,000万円以上を目指す転職エージェント比較」などのハイキャリア向け記事での紹介もおすすめです。
-</t>
+・「年収1,000万円以上を目指す転職エージェント比較」などのハイキャリア向け記事での紹介もおすすめです。</t>
   </si>
   <si>
     <t>25歳〜40代（法人営業・経営企画・コンサル出身者中心）</t>
@@ -378,18 +377,6277 @@
   <si>
     <t>SAP特化の転職支援(コンサルタント・エンジニア向け、年収1000万円超求人多数)</t>
   </si>
+  <si>
+    <t>株式会社Ｇｒｏｏｖｅｍｅｎｔ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1R3YWI+4SXU+NTRMQ" rel="nofollow"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Groovement Agent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www18.a8.net/0.gif?a8mat=4BC2EM+1R3YWI+4SXU+NTRMQ" alt=""&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>セールスポイント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・コンサルティングファーム・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・スタートアップ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>領域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>し</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>CxO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>との</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>独自</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ネットワークから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>非公開求人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提供</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>します</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界専任</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>コンサルタントによる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>企業理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をもとに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、年収交渉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最大化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伴走型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>サポートを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>います</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>取引企業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>250</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>社以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支援実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1,500</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>名以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>え</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Strategy Consultant Bank</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>との</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>連携</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>による</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特別採用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ルートを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>持</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ちます</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ターゲットユーザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・コンサルティングファーム</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>経験者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>SIer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事業会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>推進担当者</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>など</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>650</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万円</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>のプロフェッショナル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>でキャリアアップを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目指</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>している</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>第二新卒</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>からエグゼクティブまで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幅広</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>対応</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しており</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、年収向上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界転換</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>独立支援</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>視野</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>入</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>れて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>検討</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>している</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>おススメの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仕方◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ハイクラス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比較」記事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>でのご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>効果的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>コンサル・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>DX</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>領域特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>強</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>みや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>非公開求人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>へのアクセス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>差別化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ポイントとして</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>訴求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>してください</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1,000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>万円以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>目指</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>すプロフェッショナルにおすすめのエージェント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>など</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　高年収層向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>けの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職関連</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>コンテンツでのご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>もおすすめです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「無料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>面談</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>だけ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>試</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>せる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敷居</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>低</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>さと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、内定後</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伴走</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>するサポートの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>手厚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>さをあわせて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>訴求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>すると</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>がりやすいです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>ＭｙＶｉｓｉｏｎ/ITエンジニア特化</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+20MWKY+5B0Y+HVFKY" rel="nofollow"&gt;TechGO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>テックゴー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www12.a8.net/0.gif?a8mat=4BC2EM+20MWKY+5B0Y+HVFKY" alt=""&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>サービス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>テックゴーは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エンジニア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>専門</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェントです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　高年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>正社員</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ポジションを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>希望</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>される</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>求職者様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>にご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好評</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をいただいております</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>訴求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ポイント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>面接対策</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>何度</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>も</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>実施！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　大手</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェントでは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模擬面接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なし</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>回</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>まで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>となるケースも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>珍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しくないですが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>テックゴーなら</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模擬面接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>回数</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>制限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>がないため</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>プレゼンに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>慣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>れていないエンジニアの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>にも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「面接本番</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>落</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ち</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>着</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>いて</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をアピールできた</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好評</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をいただいております</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>には</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1Day</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>選考会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>への</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参加</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>がおすすめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　人気企業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特別選考会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>や</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>独占選考会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>定期的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>開催</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しております</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　特</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>土曜日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>日</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ですべての</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>面接</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>できる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1Day</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>選考会</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>平日忙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しいエンジニアの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>にご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好評</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をいただいております</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <charset val="134"/>
+      </rPr>
+      <t>※</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>事前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>弊社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>キャリアアドバイザーとの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>面談</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>のうえ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>書類選考</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>通過</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>していることが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参加条件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>となります</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>アップにこだわる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>におすすめ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>！</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>コンサル</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界／</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ハイクラス</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>求人専門</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>MyVision</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>じ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>運営会社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なので</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、高収入求人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>豊富</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　特</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>コンサルやメガベンチャーなど</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、課題解決能力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>活</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>かして</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>実現</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>できるポジションが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>人気</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+●</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>獲得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>したいユーザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ターゲットユーザーは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、実務経験</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年以上</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>IT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エンジニアの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>となります</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>代後半〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>代</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支援実績</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>豊富</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エンジニアのスキルを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>活用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>してもっと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>年収</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をアップしたい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>／大</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>きな</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>案件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>関</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>わってみたい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　特</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>におすすめのサービスとなります</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
+  <si>
+    <t>ＭｙＶｉｓｉｏｎ/メーカー・製造業特化</t>
+  </si>
+  <si>
+    <r>
+      <t>&lt;a href="https://px.a8.net/svt/ejp?a8mat=4BC2EM+1MXXO2+5B0Y+TRVYQ" rel="nofollow"&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>メーカー・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特化！経験豊富</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なコンサルが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>導</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職支援【</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>メーカーズジョブ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;/a&gt;
+&lt;img border="0" width="1" height="1" src="https://www15.a8.net/0.gif?a8mat=4BC2EM+1MXXO2+5B0Y+TRVYQ" alt=""&gt;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>セールスポイント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェントで</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、業界知識</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>さが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>他社</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>と</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>一線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>画</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しています</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界経験豊富</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なコンサルタントが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>個別対応</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、専門的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なキャリアアドバイスを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提供</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>します</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>完全無料</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>利用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>でき</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・エンジニア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ならではのキャリア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>課題</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>をしっかり</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支援</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>けられます</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ターゲットユーザー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>でのキャリアアップや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>検討</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>しているエンジニア・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技術職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大手汎用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェントでは</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自分</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>専門</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>スキルや</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界知識</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>く</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>してもらえないと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>感</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>じている</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>専門性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>したコンサルタントから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、的確</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なキャリアアドバイスを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>受</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>けたい</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>おススメの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>提案</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仕方◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エンジニア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>キャリア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>などの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>悩</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>み</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>キーワードに</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>連動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>記事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>メーカーズジョブを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>すると</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ターゲット</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>刺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>さりやすいです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>「業界特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>だから</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>深</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>い</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>理解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>得</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>られる</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>専門性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>さを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>前面</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>した</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>訴求</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>成果</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>に</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>がりやすいです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>エージェント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>比較記事</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>特化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>明確</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>な</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>差別化</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ポイントを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>強調</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>効果的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆広告主</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>からのメッセージ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>◆</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>製造業</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・メーカー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>業界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>転職</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>検討</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>している</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>最適</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>なキャリアを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>築</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>けるよう</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>　業界</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>り</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>くしたコンサルタントが</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>でサポートします</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Noto Sans"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>・メディア</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>会員様</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>には</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>、「業界特化」</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>という</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>強</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>みを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>活</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>かしてご</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>紹介</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>いただけますと</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>幸</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ ゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>いです</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <charset val="134"/>
+      </rPr>
+      <t>。</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,15 +6677,37 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="MS PGothic"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="MS PGothic"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -438,8 +6718,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="MS PGothic"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,14 +6736,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="MS PGothic"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -470,13 +6750,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="MS PGothic"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
@@ -485,7 +6758,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -495,14 +6768,6 @@
       <color rgb="FFFA7D00"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="MS PGothic"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -523,10 +6788,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="MS PGothic"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -538,11 +6803,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C6500"/>
       <name val="MS PGothic"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -555,10 +6819,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="MS PGothic"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
@@ -582,7 +6858,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -594,13 +6972,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,55 +7002,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -672,97 +7038,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -773,6 +7049,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -806,16 +7097,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -835,21 +7126,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -879,7 +7155,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -888,7 +7164,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -897,131 +7173,131 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1037,6 +7313,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2087,9 +8370,15 @@
       <c r="A19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="2"/>
+      <c r="B19" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -2118,9 +8407,15 @@
       <c r="A20" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -2149,9 +8444,15 @@
       <c r="A21" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="2"/>
+      <c r="B21" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>112</v>
+      </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
